--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_rf_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_rf_quarterly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>1.946115669774335</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -958,27 +959,27 @@
         <v>0.7822599407481463</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -986,11 +987,11 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
@@ -998,7 +999,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1006,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1095,19 +1096,19 @@
         <v>1.46786696439057</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
@@ -1115,7 +1116,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1123,19 +1124,19 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1143,7 +1144,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1236,27 +1237,27 @@
         <v>1.602192217867227</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1266,19 +1267,19 @@
         <v>-0.04409032582389416</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1286,15 +1287,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
@@ -1302,15 +1303,15 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -1393,19 +1394,19 @@
         <v>2.349078057012086</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
@@ -1413,7 +1414,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1421,19 +1422,19 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1534,27 +1535,27 @@
         <v>2.072728903209384</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1564,19 +1565,19 @@
         <v>0.03484115273627242</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1584,15 +1585,15 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
@@ -1600,15 +1601,15 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1691,19 +1692,19 @@
         <v>2.266773974242429</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
@@ -1711,7 +1712,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1719,19 +1720,19 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1739,7 +1740,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1832,27 +1833,27 @@
         <v>2.026044261723877</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="n">
@@ -1862,19 +1863,19 @@
         <v>-0.1072950483832673</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH10" s="2" t="n">
@@ -1882,15 +1883,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
@@ -1898,15 +1899,15 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -2151,28 +2152,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196766695</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208211</v>
+        <v>0.08831268540851211</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997945</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798214</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2181,10 +2182,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278878</v>
+        <v>0.272403402144199</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2193,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.139529174066894</v>
+        <v>-0.08310591627222996</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2239,49 +2240,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.06044405831575084</v>
+        <v>0.09065154909918771</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.169733991897312</v>
+        <v>0.03238372289859548</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2210688962956472</v>
+        <v>0.08644743295588117</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2075031531618561</v>
+        <v>0.3107776446448876</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9855955678670361</v>
+        <v>0.9</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4893559340541899</v>
+        <v>-0.1757126481189498</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.03568578730644023</v>
+        <v>-0.007207275939795976</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.040167367540651</v>
+        <v>1.035256243298725</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4938733180213994</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.076679489756934</v>
+        <v>0.3231448312415395</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.2130216235535571</v>
+        <v>0.03987841356902466</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.512213984054911</v>
+        <v>1.186273110753881</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1510881223581858</v>
+        <v>-0.07734267826577679</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2333,58 +2334,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.3232523550594082</v>
+        <v>0.07226254240722541</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4596274527008404</v>
+        <v>0.01497714496384162</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1029240628466189</v>
+        <v>0.080664311843716</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1531765783358609</v>
+        <v>0.2791637973599133</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2531143766379184</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.4104392274304347</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.538015984914983</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.7716934342675263</v>
+        <v>0.2794607860995721</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.03487440246540663</v>
+        <v>0.005546498809638756</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.083856072122412</v>
+        <v>1.0259078407238</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.05531518128978974</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.2478285343604663</v>
+        <v>-0.01686056991084872</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.4626344907753057</v>
+        <v>0.01670631053711547</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1468623622440189</v>
+        <v>-0.03301531632102395</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2435,58 +2436,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.07068701596020799</v>
+        <v>-0.1294595697753161</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.1810325942519855</v>
+        <v>-0.175968006434867</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1759931954029403</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1142643694716532</v>
+        <v>0.1127918881739868</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1111064348639102</v>
+        <v>0.2737689564221251</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9789473684210527</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1289388363949661</v>
+        <v>-0.1757126481189498</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.6449357119893826</v>
+        <v>-0.007207275939795976</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.2740703865907442</v>
+        <v>1.035256243298725</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1759931954029403</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.229175470903775</v>
+        <v>0.05611280852251666</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2820189958526425</v>
+        <v>-0.1699858655338384</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3218807037749891</v>
+        <v>0.2059915848364217</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07727029715116973</v>
+        <v>-0.05872004601056802</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.009659121161681661</v>
+        <v>-0.2018161703949372</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.7058088435663354</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.4081053542606882</v>
+        <v>-0.201816170394937</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2541,67 +2542,67 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.07675503289535324</v>
+        <v>0.06651763441643865</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1877259842679768</v>
+        <v>0.009539157456156744</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4133894374417633</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1891008726791924</v>
+        <v>0.08540780659841282</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.170230925144417</v>
+        <v>0.3030455746597889</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9811634349030471</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3749185176576233</v>
+        <v>-0.1757126481189498</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.180420957987357</v>
+        <v>-0.007207275939795976</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7969209739081005</v>
+        <v>1.035256243298725</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4133894374417633</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7225834764140089</v>
+        <v>0.2938663100708887</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.006188492529881184</v>
+        <v>0.01686800576807745</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.014880331682513</v>
+        <v>1.078790895259554</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.06488723706027</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.01538126830142117</v>
+        <v>-0.02212797909899111</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2241040756727617</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1705106710445579</v>
+        <v>-0.022127979098991</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1862814158021947</v>
+        <v>-0.00535774380208176</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.1630827227218641</v>
+        <v>-0.01643179585291432</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.02771921874498628</v>
+        <v>0.0112590586032979</v>
       </c>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
@@ -2649,58 +2650,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.316874183774169</v>
+        <v>-0.1294595697753161</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.246470870654807</v>
+        <v>-0.175968006434867</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.6352434573939332</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.4353947063542998</v>
+        <v>0.1127918881739868</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1853787160636058</v>
+        <v>0.2737689564221251</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9983379501385041</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.5940756832988094</v>
+        <v>-0.1757126481189498</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.2334414243160529</v>
+        <v>-0.007207275939795976</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.262758038913262</v>
+        <v>1.035256243298725</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.6149742304493668</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.682889612963725</v>
+        <v>0.05611280852251666</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.01699732643018015</v>
+        <v>-0.1699858655338384</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.9591296501085229</v>
+        <v>0.2059915848364217</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1314518703122517</v>
+        <v>-0.05872004601056802</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.3558115481255986</v>
+        <v>-0.2018161703949372</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.2050738591285862</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.189624772977991</v>
+        <v>-0.201816170394937</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2755,67 +2756,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.155129072161197</v>
+        <v>0.06651763441643865</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.06805622106224596</v>
+        <v>0.009539157456156744</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.5593831896735858</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.3373920470620719</v>
+        <v>0.08540780659841282</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1944549506743274</v>
+        <v>0.3030455746597889</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9983379501385041</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.5554505076287066</v>
+        <v>-0.1757126481189498</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1605005867534397</v>
+        <v>-0.007207275939795976</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.180656965846235</v>
+        <v>1.035256243298725</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.5593831896735858</v>
+        <v>-0.1791526234291336</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.9005103871160336</v>
+        <v>0.2938663100708887</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.1101184399089543</v>
+        <v>0.01686800576807745</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.264781592979906</v>
+        <v>1.078790895259554</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1314518703122516</v>
+        <v>-0.06488723706027</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.2032857167584414</v>
+        <v>-0.02212797909899111</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-0.1294337445243724</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.08483210987051248</v>
+        <v>-0.022127979098991</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.3615194224983095</v>
+        <v>-0.00535774380208176</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.4047957565842972</v>
+        <v>-0.01643179585291432</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.07270837626700599</v>
+        <v>0.0112590586032979</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -2863,64 +2864,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.1153994964781399</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.02423209399425186</v>
+        <v>-0.03796582501302315</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.4394409730279956</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.3049067843616645</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1340122941224851</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9950138504155125</v>
+        <v>0</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.4129392333983349</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1086215990784438</v>
+        <v>0.2117597153840087</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.8777372163441184</v>
+        <v>-0.03587709265072071</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.4394409730279956</v>
+        <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.5068295376687693</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1198368254624769</v>
+        <v>-0.2060850325577076</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.7118503897272391</v>
+        <v>0.03737143334716841</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.08706740725987905</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1658206799453185</v>
+        <v>-0.06814282940658944</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1496476817258547</v>
+        <v>0.220556603626485</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2744043820430194</v>
+        <v>-0.2365309664257261</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.05843080957065849</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.05333835813334986</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2969,70 +2974,74 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.07525418330550993</v>
+        <v>0.07226254240722541</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.02005061669203489</v>
+        <v>0.01497714496384162</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.5369583225836583</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.2906344506301834</v>
+        <v>0.080664311843716</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1777900938991522</v>
+        <v>0.2791637973599133</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9966759002770084</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.4995073183894014</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.05485593897525076</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.061744992304227</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.5369583225836583</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.8476710063344659</v>
+        <v>0.2794607860995721</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.07925411453791509</v>
+        <v>0.005546498809638756</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1.190567816933399</v>
+        <v>1.0259078407238</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.05531518128978974</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.1279636021882977</v>
+        <v>-0.01686056991084872</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>-0.0198795697672689</v>
+        <v>0.01670631053711547</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.1102762773706943</v>
+        <v>-0.03301531632102395</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.3011568706764379</v>
+        <v>0</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.329893807089703</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.04288415286606906</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.05843080957065849</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.01735760353059468</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3275,28 +3284,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.05341499464255506</v>
+        <v>-0.09123360655355239</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2216991067360366</v>
+        <v>0.2716992530341484</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389480542019927</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4707583434268603</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3305,10 +3314,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.12172130237064</v>
+        <v>0.7171104771509207</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -3317,7 +3326,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756415</v>
+        <v>-0.139529174066894</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3363,49 +3372,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.01148643596579624</v>
+        <v>0.05839323605780855</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.03980250792897255</v>
+        <v>0.1646483009169268</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.4938733180213996</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2469922875836444</v>
+        <v>0.2211914060841004</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2840766821769304</v>
+        <v>0.2076175838581398</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9941860465116279</v>
+        <v>0.9866888519134775</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.5638362806438031</v>
+        <v>-0.4900454549092432</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.1215068521088731</v>
+        <v>-0.03644292024794071</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.119813146320841</v>
+        <v>1.040970301964238</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.5638362806438034</v>
+        <v>-0.4938733180213996</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.319052206952952</v>
+        <v>1.075465835625498</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.09300510126463379</v>
+        <v>0.2086967398097597</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.175917943401159</v>
+        <v>1.499721270142814</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1907361417385124</v>
+        <v>-0.1510881223581858</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3457,58 +3466,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.2802901328432288</v>
+        <v>0.3294578948487177</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.21537109245123</v>
+        <v>0.4629259009092757</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1663071666219633</v>
+        <v>0.1029808820995737</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2118385751587301</v>
+        <v>0.1532558675077065</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9462209302325582</v>
+        <v>0.9484193011647255</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.4439839127181155</v>
+        <v>-0.2514292974161799</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1198921439760285</v>
+        <v>0.414421357968767</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.8817790541059516</v>
+        <v>0.5340941927569753</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.302613471315189</v>
+        <v>0.7759950933958086</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.08525727141563522</v>
+        <v>0.03429285245675695</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.16126302367821</v>
+        <v>1.082113730200731</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1209745732692815</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.2657511631589711</v>
+        <v>0.2561095909876958</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.2747875685364125</v>
+        <v>0.467916522737525</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.007088557811884111</v>
+        <v>-0.1442908561004745</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -3559,68 +3568,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.0445985744042422</v>
+        <v>0.06904102771382914</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.09304364333645665</v>
+        <v>0.1763650542352788</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2593752373510614</v>
+        <v>-0.1759931954029403</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.09683755729827484</v>
+        <v>0.1143253909332888</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.09698091668426975</v>
+        <v>0.1111669753041809</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3590116279069768</v>
+        <v>0.9794786466999446</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>-0.1301150271673394</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.058870045499049</v>
+        <v>0.6436441879220158</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.04411026616389809</v>
+        <v>0.2763945216991248</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1759931954029403</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>-0.06535692893279632</v>
+        <v>0.228945275641036</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.5594882937627534</v>
+        <v>-0.284294579763943</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-0.05826485491063718</v>
+        <v>0.3192608153636736</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.2593752373510615</v>
+        <v>-0.07727029715116973</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.05544810921412591</v>
+        <v>0.01006033607667445</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>1.343638138147673</v>
+        <v>0.7058088435663357</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.5969719576536617</v>
+        <v>-0.4078701491751322</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.1285602973317337</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.09292888339844574</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3669,74 +3674,70 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1094567771378301</v>
+        <v>0.07791191787960705</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.05320009946724857</v>
+        <v>0.1861265179400882</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.4133894374417632</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1719776878290576</v>
+        <v>0.1892056581486244</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2198177068509925</v>
+        <v>0.1703221651414754</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9745639534883721</v>
+        <v>0.9816971713810316</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.4439839127181155</v>
+        <v>-0.3757625629465554</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1198921439760285</v>
+        <v>0.1794941484678403</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.8817790541059516</v>
+        <v>0.7982069106013329</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.4133894374417632</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.9953681242596257</v>
+        <v>0.7267658969119482</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.05955220318985222</v>
+        <v>0.005623062633132392</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.8873577796517013</v>
+        <v>1.013464340668105</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1907685898653634</v>
+        <v>-0.1209745732692815</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.09685779036521525</v>
+        <v>0.01844180514087523</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2747875685364125</v>
+        <v>0.2241040756727619</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1395760223607132</v>
+        <v>-0.1680104450423102</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1334333143113563</v>
+        <v>-0.1892094348709965</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.166094218089511</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.1334333143113564</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1285602973317337</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.003879815783991547</v>
-      </c>
+        <v>-0.02771921874498617</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3781,58 +3782,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.05133810366086111</v>
+        <v>-0.3181952997895825</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.001971579094902309</v>
+        <v>-0.2497470140541731</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.316876237017826</v>
+        <v>-0.6352434573939333</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.122507033751031</v>
+        <v>0.4355696414348659</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1670828080487791</v>
+        <v>0.1854804013972565</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9723837209302325</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.316876237017826</v>
+        <v>-0.5946238014511673</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.375904318285009</v>
+        <v>-0.2340432890833664</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.6293354793772264</v>
+        <v>1.263118986107894</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.316876237017826</v>
+        <v>-0.6149742304493669</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5390155644289829</v>
+        <v>0.6819060977214368</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.274638208746167</v>
+        <v>-0.020502105075904</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.4805253883382888</v>
+        <v>0.9509080113159819</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.259375237351062</v>
+        <v>-0.1314518703122517</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.03939911231435689</v>
+        <v>-0.3558115481255987</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.5662095049778659</v>
+        <v>-0.2050738591285862</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.3363601044363183</v>
+        <v>-0.1896247729779911</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3887,67 +3888,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.06920300705111249</v>
+        <v>-0.1567629915464895</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.01498745744920282</v>
+        <v>-0.07210806370647194</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4803090186007117</v>
+        <v>-0.5593831896735858</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.183334047179874</v>
+        <v>0.3375573111602926</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.235483493262901</v>
+        <v>0.1945619153000044</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>0.9988907376594565</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4803090186007117</v>
+        <v>-0.5560507812175628</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.04672843228220991</v>
+        <v>-0.1611597211432191</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.9539229237100524</v>
+        <v>1.181180937059598</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4803090186007117</v>
+        <v>-0.5593831896735858</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.057382262382621</v>
+        <v>0.899399689825221</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.03032398266262937</v>
+        <v>0.1061604451780878</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.9426425798885651</v>
+        <v>1.254199622627932</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1907685898653633</v>
+        <v>-0.1314518703122516</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.05706114193237477</v>
+        <v>-0.2032857167584416</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1915043785998121</v>
+        <v>-0.1294337445243724</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1128348658067271</v>
+        <v>-0.0848321098705126</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.1648744455472296</v>
+        <v>-0.3657286840592537</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.06533103396373563</v>
+        <v>-0.4069374913417392</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.1065012482501017</v>
+        <v>0.06948476202907483</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -3995,58 +3996,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.02183159099047138</v>
+        <v>-0.1171102499948232</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.07143109412312776</v>
+        <v>-0.02847447223827793</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2290574595209739</v>
+        <v>-0.4394409730279956</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1191837763734946</v>
+        <v>0.30505491640931</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1299241626254453</v>
+        <v>0.134085368634117</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9847383720930233</v>
+        <v>0.9955629506378258</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.06868270925283737</v>
+        <v>-0.4137319394508485</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.875799893768231</v>
+        <v>0.1077511629474897</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.1364080379120681</v>
+        <v>0.8788626802429222</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1063291499667162</v>
+        <v>-0.4394409730279956</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.05030629059273584</v>
+        <v>0.5059489155492845</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.5049744330609263</v>
+        <v>-0.1229749421551498</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.04484740593444983</v>
+        <v>0.7055383119758883</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.229057459520974</v>
+        <v>-0.08706740725987905</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.03293966757394484</v>
+        <v>-0.1658206799453185</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>1.135247040083575</v>
+        <v>0.149647681725855</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.5470967460569791</v>
+        <v>-0.2744043820430195</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4101,67 +4102,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.08232008037697458</v>
+        <v>-0.0770425749598781</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.02743940980660486</v>
+        <v>0.01561570904911602</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.4564161498649841</v>
+        <v>-0.5369583225836583</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.189077040045165</v>
+        <v>0.2907866527179535</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2249978246745735</v>
+        <v>0.1778878088761859</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9818313953488372</v>
+        <v>0.9972268441486412</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.4564161498649841</v>
+        <v>-0.5001831318665108</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.09485192476063276</v>
+        <v>-0.05559802043961748</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.9064702332179901</v>
+        <v>1.062505081111158</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.4564161498649841</v>
+        <v>-0.5369583225836583</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.9910821120019422</v>
+        <v>0.8465911894626608</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.06157226692437512</v>
+        <v>0.07540616287344437</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.8835368552842799</v>
+        <v>1.180558946546377</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.1907685898653634</v>
+        <v>-0.1209745732692815</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.07002925782543423</v>
+        <v>-0.1279636021882978</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.246283966344971</v>
+        <v>-0.01987956976726879</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.1414241964746177</v>
+        <v>-0.1102762773706945</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.1546290542961606</v>
+        <v>-0.3057640797679061</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.0223594918047143</v>
+        <v>-0.3323050629575995</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.1352946828437117</v>
+        <v>0.0397501639105704</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -4407,28 +4408,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.05341499464255506</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.08126757478702572</v>
+        <v>0.2216991067360366</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962868</v>
+        <v>0.2389480542019927</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4437,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.12172130237064</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4449,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756415</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4495,49 +4496,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.08718588803191984</v>
+        <v>0.01148643596579624</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.06231718026233857</v>
+        <v>-0.03980250792897255</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.04200401516810738</v>
+        <v>0.2469922875836444</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1767962239874382</v>
+        <v>0.2840766821769304</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.8206896551724138</v>
+        <v>0.9941860465116279</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.140631790481074</v>
+        <v>-0.5638362806438031</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.06811781052202481</v>
+        <v>-0.1215068521088731</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7195765616634978</v>
+        <v>1.119813146320841</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.5638362806438034</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2650990297168732</v>
+        <v>1.319052206952952</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.005430702683303479</v>
+        <v>0.09300510126463379</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.9746039866510305</v>
+        <v>1.175917943401159</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.02856338737954378</v>
+        <v>-0.1907361417385124</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4589,58 +4590,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.02427859728711668</v>
+        <v>0.2802901328432288</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.0008488550590588506</v>
+        <v>0.21537109245123</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04278454166173134</v>
+        <v>0.1663071666219633</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1644125150610335</v>
+        <v>0.2118385751587301</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9241379310344827</v>
+        <v>0.9462209302325582</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181155</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.1198921439760285</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.8817790541059516</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1881819355445027</v>
+        <v>1.302613471315189</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06589978732071489</v>
+        <v>0.08525727141563522</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6918277475147857</v>
+        <v>1.16126302367821</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1240889646699911</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.05786249751519601</v>
+        <v>0.2657511631589711</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.003126882001617481</v>
+        <v>0.2747875685364125</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.06079926738192531</v>
+        <v>-0.007088557811884111</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -4691,67 +4692,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.08571925308322292</v>
+        <v>-0.0445985744042422</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.06088409368503367</v>
+        <v>-0.09304364333645665</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1492975281333246</v>
+        <v>-0.2593752373510614</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04199968097956676</v>
+        <v>0.09683755729827484</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.17653628544757</v>
+        <v>0.09698091668426975</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.3590116279069768</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1417910949420261</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.06667689878146388</v>
+        <v>1.058870045499049</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7255084232651985</v>
+        <v>-0.04411026616389809</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1492975281333246</v>
+        <v>0</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2650990297168732</v>
+        <v>-0.06535692893279632</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.005430702683303479</v>
+        <v>-0.5594882937627534</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.9746039866510305</v>
+        <v>-0.05826485491063718</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02856338737954378</v>
+        <v>-0.2593752373510615</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.001349019486770464</v>
+        <v>-0.05544810921412591</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-0.001349019486770575</v>
+        <v>1.343638138147673</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.5969719576536617</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.148410030246944</v>
+        <v>0.1285602973317337</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1211258743527557</v>
+        <v>-0.09292888339844574</v>
       </c>
     </row>
     <row r="6">
@@ -4801,73 +4802,73 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.07944896321447104</v>
+        <v>0.1094567771378301</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.05475723283618827</v>
+        <v>0.05320009946724857</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.04204158925417218</v>
+        <v>0.1719776878290576</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1769856922822356</v>
+        <v>0.2198177068509925</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.8344827586206897</v>
+        <v>0.9745639534883721</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1467474578207134</v>
+        <v>-0.4439839127181155</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.06051658308966079</v>
+        <v>0.1198921439760285</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7508688524142703</v>
+        <v>0.8817790541059516</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2650990297168732</v>
+        <v>0.9953681242596257</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.005430702683303479</v>
+        <v>-0.05955220318985222</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.9746039866510305</v>
+        <v>0.8873577796517013</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02856338737954378</v>
+        <v>-0.1907685898653634</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.007116469136160819</v>
+        <v>0.09685779036521525</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-0.007116469136161041</v>
+        <v>0.2747875685364125</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1395760223607132</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.05386265618892883</v>
+        <v>-0.1334333143113563</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.01021142122852803</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0.06473511494443152</v>
+        <v>-0.1334333143113564</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.148410030246944</v>
+        <v>0.1285602973317337</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.01497703503645686</v>
+        <v>-0.003879815783991547</v>
       </c>
     </row>
     <row r="7">
@@ -4913,58 +4914,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.03856349909548251</v>
+        <v>0.05133810366086111</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.06055576706290966</v>
+        <v>-0.001971579094902309</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.316876237017826</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.06860173054297604</v>
+        <v>0.122507033751031</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1471441229428625</v>
+        <v>0.1670828080487791</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9724137931034482</v>
+        <v>0.9723837209302325</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.140631790481074</v>
+        <v>-0.316876237017826</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.06811781052202481</v>
+        <v>0.375904318285009</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7195765616634978</v>
+        <v>0.6293354793772264</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.316876237017826</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.1187713139199429</v>
+        <v>0.5390155644289829</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1204675891716919</v>
+        <v>-0.274638208746167</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.4366481317181137</v>
+        <v>0.4805253883382888</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.003773856814325405</v>
+        <v>-0.259375237351062</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.1156650288710428</v>
+        <v>0.03939911231435689</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.5662095049778659</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1156650288710427</v>
+        <v>-0.3363601044363183</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5019,67 +5020,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.04605963543944069</v>
+        <v>0.06920300705111249</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.02213166537501099</v>
+        <v>0.01498745744920282</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4803090186007117</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04640144669379589</v>
+        <v>0.183334047179874</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1664250001569836</v>
+        <v>0.235483493262901</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.140631790481074</v>
+        <v>-0.4803090186007117</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.06811781052202481</v>
+        <v>0.04672843228220991</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7195765616634978</v>
+        <v>0.9539229237100524</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4803090186007117</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2172426485557624</v>
+        <v>1.057382262382621</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.04305343913752235</v>
+        <v>-0.03032398266262937</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7986658856473314</v>
+        <v>0.9426425798885651</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1907685898653633</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03782816999853444</v>
+        <v>0.05706114193237477</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>0.1915043785998121</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03782816999853444</v>
+        <v>-0.1128348658067271</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.02126475961717134</v>
+        <v>-0.1648744455472296</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.003117135088014145</v>
+        <v>-0.06533103396373563</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.02445813401290442</v>
+        <v>-0.1065012482501017</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -5127,58 +5128,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.03856349909548251</v>
+        <v>-0.02183159099047138</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.06055576706290966</v>
+        <v>-0.07143109412312776</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.2290574595209739</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06860173054297604</v>
+        <v>0.1191837763734946</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1471441229428625</v>
+        <v>0.1299241626254453</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9724137931034482</v>
+        <v>0.9847383720930233</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.140631790481074</v>
+        <v>-0.06868270925283737</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.06811781052202481</v>
+        <v>0.875799893768231</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7195765616634978</v>
+        <v>0.1364080379120681</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.1063291499667162</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1187713139199429</v>
+        <v>0.05030629059273584</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1204675891716919</v>
+        <v>-0.5049744330609263</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.4366481317181137</v>
+        <v>0.04484740593444983</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.003773856814325405</v>
+        <v>-0.229057459520974</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.1156650288710428</v>
+        <v>-0.03293966757394484</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>1.135247040083575</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1156650288710427</v>
+        <v>-0.5470967460569791</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5233,67 +5234,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.04605963543944069</v>
+        <v>0.08232008037697458</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.02213166537501099</v>
+        <v>0.02743940980660486</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4564161498649841</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.04640144669379589</v>
+        <v>0.189077040045165</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1664250001569836</v>
+        <v>0.2249978246745735</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9818313953488372</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.140631790481074</v>
+        <v>-0.4564161498649841</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.06811781052202481</v>
+        <v>0.09485192476063276</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7195765616634978</v>
+        <v>0.9064702332179901</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1492975281333249</v>
+        <v>-0.4564161498649841</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.2172426485557624</v>
+        <v>0.9910821120019422</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.04305343913752235</v>
+        <v>-0.06157226692437512</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7986658856473314</v>
+        <v>0.8835368552842799</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1907685898653634</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.03782816999853444</v>
+        <v>0.07002925782543423</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0</v>
+        <v>0.246283966344971</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.03782816999853444</v>
+        <v>-0.1414241964746177</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.02126475961717134</v>
+        <v>-0.1546290542961606</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.003117135088014145</v>
+        <v>-0.0223594918047143</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.02445813401290442</v>
+        <v>-0.1352946828437117</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -5539,28 +5540,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.0189121018756262</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.0809929380075199</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4590501973559848</v>
+        <v>0.2138559415886582</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5569,10 +5570,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5581,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.0518515658788602</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5627,49 +5628,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.008436531833865168</v>
+        <v>0.08432370578342496</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.09679398940886819</v>
+        <v>0.06419749435440836</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1369242220207967</v>
+        <v>0.04186991637394554</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4907777251471288</v>
+        <v>0.176236075214825</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.8287671232876712</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.321442164673614</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.04398902844387387</v>
+        <v>0.07000839179890761</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.107582492397094</v>
+        <v>0.7181593923941526</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.4612806993661687</v>
+        <v>0.2650990297168732</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.05523468091484574</v>
+        <v>-0.005430702683303479</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.8437348117057034</v>
+        <v>0.9746039866510305</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.09747854570857184</v>
+        <v>-0.02856338737954378</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5721,58 +5722,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.007037250069187984</v>
+        <v>0.02497427700722055</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08269906430310359</v>
+        <v>0.005949654656603798</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1167974844615735</v>
+        <v>0.04263876767180749</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4296396949184721</v>
+        <v>0.1638459834801125</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.07691834452240665</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.6903412233993171</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.418854880877529</v>
+        <v>0.1881819355445027</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08266434720637639</v>
+        <v>-0.06589978732071489</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7661331690981564</v>
+        <v>0.6918277475147857</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07820336667939509</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.01560543767477784</v>
+        <v>-0.0547340507817492</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.04597351304004449</v>
+        <v>0.006457849093951529</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.0290333120166727</v>
+        <v>-0.06079926738192531</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5823,64 +5824,68 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.258670034247109</v>
+        <v>0.08581180328146543</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.3247293769932001</v>
+        <v>0.06565797116619709</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333249</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2453237676003178</v>
+        <v>0.04185658113943472</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4142337056157518</v>
+        <v>0.175927625878694</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.7876712328767124</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.321442164673614</v>
+        <v>-0.1417179384569854</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.04398902844387387</v>
+        <v>0.07147684333439064</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.107582492397094</v>
+        <v>0.7122476829209644</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333249</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.09250815060784245</v>
+        <v>0.2650990297168732</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2936580822836764</v>
+        <v>-0.005430702683303479</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.1692079186092115</v>
+        <v>0.9746039866510305</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.06035805831057006</v>
+        <v>-0.02856338737954378</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2523625672454863</v>
+        <v>0.001372373849343633</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.001372373849343633</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2523625672454864</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1514413748399237</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.1235143586481885</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5929,70 +5934,74 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.03815264527066697</v>
+        <v>0.08018211409215614</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1238621228458197</v>
+        <v>0.06013277504874392</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333246</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1504691362334638</v>
+        <v>0.04189834662563648</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4634359879895285</v>
+        <v>0.1763744535374291</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.8287671232876712</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.321442164673614</v>
+        <v>-0.1461679372768953</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.04398902844387387</v>
+        <v>0.06592147767775924</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.107582492397094</v>
+        <v>0.7346125393603897</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333246</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.4174876549272839</v>
+        <v>0.2650990297168732</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08354830308268746</v>
+        <v>-0.005430702683303479</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7636323574854567</v>
+        <v>0.9746039866510305</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.0782033666793952</v>
+        <v>-0.02856338737954378</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.02996894741570177</v>
+        <v>-0.003819515951905217</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>-0.003819515951905106</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.02996894741570189</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.04487410504105005</v>
+        <v>0.0538626561889286</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.04395284628807283</v>
+        <v>-0.01021142122852803</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.0009636122542704406</v>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
+        <v>0.06473511494443152</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.1514413748399237</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>0.01161787289546434</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6037,58 +6046,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.258670034247109</v>
+        <v>-0.04109462695157118</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3247293769932001</v>
+        <v>-0.05889293955458597</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2453237676003178</v>
+        <v>0.06837351377817279</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4142337056157518</v>
+        <v>0.1466687637042413</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.321442164673614</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.04398902844387387</v>
+        <v>0.07000839179890761</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.107582492397094</v>
+        <v>0.7181593923941526</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.09250815060784245</v>
+        <v>0.1187713139199429</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2936580822836764</v>
+        <v>-0.1204675891716919</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.1692079186092115</v>
+        <v>0.4366481317181137</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.06035805831057006</v>
+        <v>-0.003773856814325405</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2523625672454863</v>
+        <v>-0.1156650288710429</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2523625672454864</v>
+        <v>-0.1156650288710427</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6143,67 +6152,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.03815264527066697</v>
+        <v>0.04330572430760871</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1238621228458197</v>
+        <v>0.0239408506259553</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1504691362334638</v>
+        <v>0.04625151086171631</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4634359879895285</v>
+        <v>0.1658953040050387</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.321442164673614</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.04398902844387387</v>
+        <v>0.07000839179890761</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.107582492397094</v>
+        <v>0.7181593923941526</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4174876549272839</v>
+        <v>0.2172426485557624</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.08354830308268746</v>
+        <v>-0.04305343913752235</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.7636323574854567</v>
+        <v>0.7986658856473314</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.0782033666793952</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.02996894741570177</v>
+        <v>-0.03782816999853444</v>
       </c>
       <c r="Z8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.02996894741570189</v>
+        <v>-0.03782816999853444</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.04487410504105005</v>
+        <v>0.01788478765917256</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.04395284628807283</v>
+        <v>-0.006416412867925936</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>-0.0009636122542704406</v>
+        <v>0.02445813401290442</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -6251,58 +6260,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.258670034247109</v>
+        <v>-0.04109462695157118</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.3247293769932001</v>
+        <v>-0.05889293955458597</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2453237676003178</v>
+        <v>0.06837351377817279</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4142337056157518</v>
+        <v>0.1466687637042413</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.9794520547945206</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.321442164673614</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-0.04398902844387387</v>
+        <v>0.07000839179890761</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.107582492397094</v>
+        <v>0.7181593923941526</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.09250815060784245</v>
+        <v>0.1187713139199429</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2936580822836764</v>
+        <v>-0.1204675891716919</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.1692079186092115</v>
+        <v>0.4366481317181137</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.06035805831057006</v>
+        <v>-0.003773856814325405</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.2523625672454863</v>
+        <v>-0.1156650288710429</v>
       </c>
       <c r="Z9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2523625672454864</v>
+        <v>-0.1156650288710427</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -6357,67 +6366,67 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.03815264527066697</v>
+        <v>0.04330572430760871</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.1238621228458197</v>
+        <v>0.0239408506259553</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1504691362334638</v>
+        <v>0.04625151086171631</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4634359879895285</v>
+        <v>0.1658953040050387</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.321442164673614</v>
+        <v>-0.1428942080320033</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>-0.04398902844387387</v>
+        <v>0.07000839179890761</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.107582492397094</v>
+        <v>0.7181593923941526</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.3214421646736139</v>
+        <v>-0.1492975281333248</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4174876549272839</v>
+        <v>0.2172426485557624</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.08354830308268746</v>
+        <v>-0.04305343913752235</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.7636323574854567</v>
+        <v>0.7986658856473314</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.0782033666793952</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.02996894741570177</v>
+        <v>-0.03782816999853444</v>
       </c>
       <c r="Z10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.02996894741570189</v>
+        <v>-0.03782816999853444</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>-0.04487410504105005</v>
+        <v>0.01788478765917256</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>-0.04395284628807283</v>
+        <v>-0.006416412867925936</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>-0.0009636122542704406</v>
+        <v>0.02445813401290442</v>
       </c>
       <c r="AE10" s="2" t="inlineStr"/>
       <c r="AF10" s="2" t="inlineStr"/>
@@ -6663,28 +6672,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393833</v>
+        <v>0.1113578145363061</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.179974191375289</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.451830499217423</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450096</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -6693,10 +6702,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241683001</v>
+        <v>0.5657770181230009</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6705,7 +6714,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.0518515658788602</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6751,49 +6760,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.1397885555120524</v>
+        <v>-0.01801583075704949</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.07424152247084126</v>
+        <v>-0.1164104337965486</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3454801967968263</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1818140869661326</v>
+        <v>0.1347774917962256</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2520711548688638</v>
+        <v>0.4829467702160691</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9434697855750487</v>
+        <v>1</v>
       </c>
       <c r="P3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.343396896459686</v>
+        <v>-0.321442164673614</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.04863387549496068</v>
+        <v>-0.04398902844387387</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.108335005804564</v>
+        <v>1.107582492397094</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3433968964596861</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.7358866404475835</v>
+        <v>0.4471635549983983</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.1291567933740858</v>
+        <v>-0.07575373871995661</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.369524514448298</v>
+        <v>0.7903529847887605</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1077622875732581</v>
+        <v>-0.09747854570857184</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6845,58 +6854,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.06128603667882748</v>
+        <v>0.009125074064342265</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.0002535315041187758</v>
+        <v>-0.09198904181424106</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1145251377344681</v>
+        <v>0.1149439295311541</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1732872931401137</v>
+        <v>0.4227552867946717</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.237660847618366</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1045693220900867</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7670652811375739</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.3921442095204601</v>
+        <v>0.4217964992394458</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09444023883315877</v>
+        <v>-0.09195467631537591</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7298014104598676</v>
+        <v>0.7455172015271687</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07741687217408433</v>
+        <v>-0.07820336667939509</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.06887463332877342</v>
+        <v>0.02763884151240004</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1610349513598179</v>
+        <v>0.04597351304004449</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1980212433909234</v>
+        <v>-0.01752881052824784</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -6947,68 +6956,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.1677066698263883</v>
+        <v>-0.258657808496695</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2155702478111319</v>
+        <v>-0.3329401370047353</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3016712444576485</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2254387967338578</v>
+        <v>0.2457549203307299</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2089366329852145</v>
+        <v>0.4076099249974274</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8791423001949318</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2873459179370068</v>
+        <v>-0.321442164673614</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.0325795728185112</v>
+        <v>-0.04398902844387387</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.9274269596144081</v>
+        <v>1.107582492397094</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2993205153813662</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1678784295520859</v>
+        <v>0.09252616786411405</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2403202882972956</v>
+        <v>-0.3022466448167719</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.312430763220303</v>
+        <v>0.1635382224804308</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1119823433294362</v>
+        <v>-0.06035805831057006</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2697826924576355</v>
+        <v>-0.2450568810342082</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.08536508313844382</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.3272150367774255</v>
+        <v>-0.2450568810342082</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.8421981963585632</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.4564389497245325</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7057,19 +7062,19 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.08744047955719569</v>
+        <v>-0.03615851050877861</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1399200107380155</v>
+        <v>-0.1327352209302934</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3188770471454476</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2066992530837863</v>
+        <v>0.1482437665725893</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2279313805002179</v>
+        <v>0.4560072873557602</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>1</v>
@@ -7078,53 +7083,49 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3167090704541826</v>
+        <v>-0.321442164673614</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.009965319922466853</v>
+        <v>-0.04398902844387387</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.022198374706055</v>
+        <v>1.107582492397094</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3167090704541826</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.3355358325177555</v>
+        <v>0.4204264387096999</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1312627662753909</v>
+        <v>-0.09282967991671143</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6244501841063334</v>
+        <v>0.7430956458862358</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1092598324968032</v>
+        <v>-0.0782033666793952</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1993606919198841</v>
+        <v>-0.01847553180589057</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.04064529372707226</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.230631884940713</v>
+        <v>-0.01847553180589045</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.1401380128409544</v>
+        <v>-0.04487410504105016</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>-0.103691673960154</v>
+        <v>-0.04395284628807283</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>-0.04066272489270639</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.8421981963585632</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.08861411629547622</v>
-      </c>
+        <v>-0.0009636122542704406</v>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7169,58 +7170,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.2602410768270726</v>
+        <v>-0.258657808496695</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1877670524975643</v>
+        <v>-0.3329401370047353</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1811837223339979</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.06340976526593056</v>
+        <v>0.2457549203307299</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1337063833078499</v>
+        <v>0.4076099249974274</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9161793372319688</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.06971997420236187</v>
+        <v>-0.321442164673614</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.3479024056931033</v>
+        <v>-0.04398902844387387</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.2250255864538382</v>
+        <v>1.107582492397094</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1811837223339979</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.3546900308286425</v>
+        <v>0.09252616786411405</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1188033736857942</v>
+        <v>-0.3022466448167719</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6600971746882099</v>
+        <v>0.1635382224804308</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.09226300542917365</v>
+        <v>-0.06035805831057006</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1056797076374458</v>
+        <v>-0.2450568810342082</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.416807232225519</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2195976400398201</v>
+        <v>-0.2450568810342082</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7275,67 +7276,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1362478847539406</v>
+        <v>-0.03615851050877861</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.07090446883280621</v>
+        <v>-0.1327352209302934</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2682882916008086</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1420299446247503</v>
+        <v>0.1482437665725893</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2001240266376093</v>
+        <v>0.4560072873557602</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9434697855750487</v>
+        <v>1</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2682882916008086</v>
+        <v>-0.321442164673614</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.06019257070410666</v>
+        <v>-0.04398902844387387</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.8659172761731334</v>
+        <v>1.107582492397094</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2682882916008086</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.5528627896904601</v>
+        <v>0.4204264387096999</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.01010372872315646</v>
+        <v>-0.09282967991671143</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.028907309890606</v>
+        <v>0.7430956458862358</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.09226300542917376</v>
+        <v>-0.0782033666793952</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.003106427715025784</v>
+        <v>-0.01847553180589057</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1143896586140121</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1054353703130824</v>
+        <v>-0.01847553180589045</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.07063302963044493</v>
+        <v>-0.04487410504105016</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>-0.04017561460244945</v>
+        <v>-0.04395284628807283</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0.1154467899739793</v>
+        <v>-0.0009636122542704406</v>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
@@ -7383,68 +7384,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1699081510752447</v>
+        <v>-0.258657808496695</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.1026289984088444</v>
+        <v>-0.3329401370047353</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.09226300542917365</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.01496998077824432</v>
+        <v>0.2457549203307299</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.07393521778517341</v>
+        <v>0.4076099249974274</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.321442164673614</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.465299433644307</v>
+        <v>-0.04398902844387387</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.036483651193696</v>
+        <v>1.107582492397094</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.156831583942326</v>
+        <v>0.09252616786411405</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2475060229385846</v>
+        <v>-0.3022466448167719</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2918719909334601</v>
+        <v>0.1635382224804308</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.09226300542917354</v>
+        <v>-0.06035805831057006</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.02642559921972643</v>
+        <v>-0.2450568810342082</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.5402056010840708</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.3335788426575788</v>
+        <v>-0.2450568810342082</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.1149306197576361</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.1029587147715519</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7493,74 +7490,70 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.09673859438926513</v>
+        <v>-0.03615851050877861</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.03366728126162211</v>
+        <v>-0.1327352209302934</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.1147720801117062</v>
+        <v>0.1482437665725893</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1818699338679585</v>
+        <v>0.4560072873557602</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.9571150097465887</v>
+        <v>1</v>
       </c>
       <c r="P10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.237660847618366</v>
+        <v>-0.321442164673614</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.1045693220900867</v>
+        <v>-0.04398902844387387</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.7670652811375739</v>
+        <v>1.107582492397094</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.3214421646736139</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.4386491772893066</v>
+        <v>0.4204264387096999</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.06418976103220264</v>
+        <v>-0.09282967991671143</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.816349650232675</v>
+        <v>0.7430956458862358</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.09226300542917376</v>
+        <v>-0.0782033666793952</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.03777012930564738</v>
+        <v>-0.01847553180589057</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1610349513598179</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.1712309180982213</v>
+        <v>-0.01847553180589045</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.03340528046650104</v>
+        <v>-0.04487410504105016</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>0</v>
+        <v>-0.04395284628807283</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0.03340528046650104</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.1149306197576361</v>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>-0.01368747521540192</v>
-      </c>
+        <v>-0.0009636122542704406</v>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7803,28 +7796,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003974344</v>
+        <v>0.06101703543393833</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1038210158252791</v>
+        <v>0.179974191375289</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213005002</v>
+        <v>0.240579627043532</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138072</v>
+        <v>-0.3098313187450096</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7833,10 +7826,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922787</v>
+        <v>0.5373300241683001</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7845,7 +7838,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174765</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7891,49 +7884,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.02943793469695388</v>
+        <v>0.1397885555120524</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.0271068564530339</v>
+        <v>0.07424152247084126</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.3454801967968263</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1050257154567922</v>
+        <v>0.1818140869661326</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2954859375373192</v>
+        <v>0.2520711548688638</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9434697855750487</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.343396896459686</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.02452750015344596</v>
+        <v>-0.04863387549496068</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.9151280089903778</v>
+        <v>1.108335005804564</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2051728224903451</v>
+        <v>-0.3433968964596861</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.2210982371589283</v>
+        <v>0.7358866404475835</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.05039821439516878</v>
+        <v>0.1291567933740858</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7733260585852043</v>
+        <v>1.369524514448298</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.07019594153968067</v>
+        <v>-0.1077622875732581</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7985,58 +7978,58 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>0.06128603667882748</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>0.0002535315041187758</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.1145251377344681</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.1732872931401137</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.9649122807017544</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.237660847618366</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.1045693220900867</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.7670652811375739</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.3921442095204601</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.09444023883315877</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.7298014104598676</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.07741687217408433</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.01692725981457721</v>
+        <v>-0.06887463332877342</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.06422592356769052</v>
+        <v>0.1610349513598179</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.0762555972233897</v>
+        <v>-0.1980212433909234</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -8087,67 +8080,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.1677066698263883</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.2155702478111319</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.3016712444576485</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.2254387967338578</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.2089366329852145</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>0.8791423001949318</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2873459179370068</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.0325795728185112</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.9274269596144081</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.2993205153813662</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1678784295520859</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.2403202882972956</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.312430763220303</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1119823433294362</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.04567930193600933</v>
+        <v>-0.2697826924576355</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.2653066776317685</v>
+        <v>0.08536508313844382</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1735763981794743</v>
+        <v>-0.3272150367774255</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.1157245680572492</v>
+        <v>0.8421981963585632</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.08904827568122387</v>
+        <v>-0.4564389497245325</v>
       </c>
     </row>
     <row r="6">
@@ -8197,19 +8190,19 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>-0.08744047955719569</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>-0.1399200107380155</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3188770471454476</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.2066992530837863</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.2279313805002179</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>1</v>
@@ -8218,52 +8211,52 @@
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3167090704541826</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>-0.009965319922466853</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>1.022198374706055</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.3167090704541826</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.3355358325177555</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.1312627662753909</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.6244501841063334</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.1092598324968032</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.01692725981457721</v>
+        <v>-0.1993606919198841</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.06422592356769052</v>
+        <v>0.04064529372707226</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.0762555972233897</v>
+        <v>-0.230631884940713</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1401380128409544</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>0</v>
+        <v>-0.103691673960154</v>
       </c>
       <c r="AD6" s="2" t="n">
-        <v>0</v>
+        <v>-0.04066272489270639</v>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>0.1157245680572492</v>
+        <v>0.8421981963585632</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.005987636340689106</v>
+        <v>-0.08861411629547622</v>
       </c>
     </row>
     <row r="7">
@@ -8309,68 +8302,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.2602410768270726</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>0.1877670524975643</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1811837223339979</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>0.06340976526593056</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1337063833078499</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>0.9161793372319688</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.06971997420236187</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.3479024056931033</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.2250255864538382</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1811837223339979</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.3546900308286425</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.1188033736857942</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.6600971746882099</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.09226300542917365</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.04567930193600933</v>
+        <v>0.1056797076374458</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2653066776317685</v>
+        <v>0.416807232225519</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1735763981794743</v>
+        <v>-0.2195976400398201</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.02141983290559235</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>-0.01602903048447502</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8419,74 +8408,70 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>0.1362478847539406</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>0.07090446883280621</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2682882916008086</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.1420299446247503</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.2001240266376093</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9434697855750487</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2682882916008086</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.06019257070410666</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.8659172761731334</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2682882916008086</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.5528627896904601</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>0.01010372872315646</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>1.028907309890606</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.09226300542917376</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.01692725981457721</v>
+        <v>-0.003106427715025784</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.06422592356769052</v>
+        <v>0.1143896586140121</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.0762555972233897</v>
+        <v>-0.1054353703130824</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0</v>
+        <v>0.07063302963044493</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>0</v>
+        <v>-0.04017561460244945</v>
       </c>
       <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2" t="n">
-        <v>0.02141983290559235</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>0.04352494315082356</v>
-      </c>
+        <v>0.1154467899739793</v>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8531,67 +8516,67 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1699081510752447</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>0.1026289984088444</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-0.09226300542917365</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>0.01496998077824432</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.07393521778517341</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.465299433644307</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.036483651193696</v>
       </c>
       <c r="T9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.156831583942326</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.2475060229385846</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.2918719909334601</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.09226300542917354</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.04567930193600933</v>
+        <v>0.02642559921972643</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.2653066776317685</v>
+        <v>0.5402056010840708</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1735763981794743</v>
+        <v>-0.3335788426575788</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="n">
-        <v>0.1157245680572492</v>
+        <v>0.1149306197576361</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.08904827568122387</v>
+        <v>-0.1029587147715519</v>
       </c>
     </row>
     <row r="10">
@@ -8641,73 +8626,73 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>0.09673859438926513</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>0.03366728126162211</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.1147720801117062</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.1818699338679585</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0.9571150097465887</v>
       </c>
       <c r="P10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.237660847618366</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.1045693220900867</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.7670652811375739</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.4386491772893066</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.06418976103220264</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.816349650232675</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.09226300542917376</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>-0.01692725981457721</v>
+        <v>-0.03777012930564738</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.06422592356769052</v>
+        <v>0.1610349513598179</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>-0.0762555972233897</v>
+        <v>-0.1712309180982213</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0</v>
+        <v>0.03340528046650104</v>
       </c>
       <c r="AC10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AD10" s="2" t="n">
-        <v>0</v>
+        <v>0.03340528046650104</v>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>0.1157245680572492</v>
+        <v>0.1149306197576361</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>-0.005987636340689106</v>
+        <v>-0.01368747521540192</v>
       </c>
     </row>
   </sheetData>
@@ -8721,7 +8706,1155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947872</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138072</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490121</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.02645937656591835</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.03123058497305986</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.1044778434432681</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.293858064365045</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.02452750015344596</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.9151280089903778</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.2051728224903451</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.2248456658016778</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.05442321959942975</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.7613051502332882</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.07019594153968067</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>-0.01647168923365216</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.06422592356769052</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.07582752027954121</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>0.0426547851343122</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.2653066776317685</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.1759667410545769</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1157245680572492</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.08904827568122387</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>-0.01647168923365216</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.06422592356769052</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.07582752027954121</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>0.1157245680572492</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.005987636340689106</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>0.0426547851343122</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.2653066776317685</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.1759667410545769</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.02141983290559235</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>-0.01602903048447502</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>-0.01647168923365216</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.06422592356769052</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.07582752027954121</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>0.02141983290559235</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>0.04352494315082356</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>0.0426547851343122</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.2653066776317685</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.1759667410545769</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.1157245680572492</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.08904827568122387</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>-0.01647168923365216</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.06422592356769052</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>-0.07582752027954121</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>0.1157245680572492</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>-0.005987636340689106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8827,24 +9960,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -8875,20 +10006,20 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-131</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -8922,23 +10053,23 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-120</v>
+        <v>-131</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-57</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8968,19 +10099,21 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-57</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -9013,24 +10146,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-132</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9061,21 +10192,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-132</v>
+      </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9092,37 +10225,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>-94</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0.1058171745152355</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -9149,27 +10280,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9196,25 +10325,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>59</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
+        <v>0.1059345535219079</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.4206896551724138</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9241,25 +10372,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9286,24 +10419,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>119</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -9333,27 +10464,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -9370,24 +10499,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -9397,10 +10526,10 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>0.313573407202216</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9417,37 +10546,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.4585755813953488</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9474,25 +10603,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -9519,25 +10650,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>183</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -9564,27 +10697,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-63</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.7309941520467836</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -9611,32 +10744,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.7309941520467836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>94</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
